--- a/terminology_resource.xlsx
+++ b/terminology_resource.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vanessa/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lauramenotti/Documents/Laura/RICERCA/PAPERS-PRESENTATIONS/2026/LREC/LREC26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A376B6F-8ECC-084C-A741-310B5C4DF9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49558C-2D6F-0E43-8CCA-82F76A099ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="7500" windowWidth="27640" windowHeight="11860" activeTab="1" xr2:uid="{AB8518AE-64E2-2842-81B9-E381C5C00868}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="3" xr2:uid="{AB8518AE-64E2-2842-81B9-E381C5C00868}"/>
   </bookViews>
   <sheets>
     <sheet name="Intensional Definitions" sheetId="1" r:id="rId1"/>
     <sheet name="Associative Relations" sheetId="2" r:id="rId2"/>
+    <sheet name="HERO-Concepts" sheetId="3" r:id="rId3"/>
+    <sheet name="HERO-Relations" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
   <si>
     <t>&lt;Microbiome&gt;</t>
   </si>
@@ -145,13 +147,58 @@
   </si>
   <si>
     <t>biome that consists of the microorganisms, their genomes (i.e., genes) and the surrounding environment where the microorganisms reside</t>
+  </si>
+  <si>
+    <t>HERO-mapping</t>
+  </si>
+  <si>
+    <t>HERO URI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://w3id.org/hereditary/ontology/gutbrain/schema/Domain </t>
+  </si>
+  <si>
+    <t>NCIT taxonomy of bacteria, distinguishing between "Species", "Genus", "Family", "Order", Class, "Phylum", and "Super Kingdom", and "Domain".</t>
+  </si>
+  <si>
+    <t>Class "Disease, Disorder, or Finding"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://w3id.org/brainteaser/ontology/schema/DiseaseDisorderOrFinding </t>
+  </si>
+  <si>
+    <t>Embedded in the more general relation "interact"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://w3id.org/hereditary/ontology/gutbrain/schema/interact </t>
+  </si>
+  <si>
+    <t>Embedded in the more general relation "influence"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://w3id.org/hereditary/ontology/gutbrain/schema/influence </t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>No match</t>
+  </si>
+  <si>
+    <t>No march</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://w3id.org/hereditary/ontology/gutbrain/schema/isLinkedTo </t>
+  </si>
+  <si>
+    <t>Embedded in the more general relation "is linked to"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -172,6 +219,35 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -190,18 +266,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -755,4 +843,236 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CB53F6-A0C1-AA4D-A032-91312ABAD6CE}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{11511695-63A7-524B-9AAB-4F53A91598B0}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{9BEF0CF9-1C63-C842-B0BE-1ABC742BB478}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{90BBFA6C-33FF-E149-B8F2-7EC77B3F5268}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{505E1A10-DF5B-8F45-88FE-A537F0B4C81B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D823EA9-733A-7647-A094-3C300700364D}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="55.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{321490EC-0C40-294C-B252-F9269E0C49C1}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{A78F2740-5494-8E40-8C74-D54F4080D2D4}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{74A858AB-364B-2D41-8719-B3E1511AB83E}"/>
+    <hyperlink ref="C2" r:id="rId4" xr:uid="{73CC3395-A088-B440-9034-B4DEDEC64AEE}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{0D8A5F39-C9C2-9549-85B3-F6AFB9BC41F1}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{6C7424E7-FCD3-5947-949C-9B7CE8FAEBEF}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{2C59D4FB-F739-A34F-A317-6059072E1F8C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/terminology_resource.xlsx
+++ b/terminology_resource.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lauramenotti/Documents/Laura/RICERCA/PAPERS-PRESENTATIONS/2026/LREC/LREC26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vanessa/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49558C-2D6F-0E43-8CCA-82F76A099ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4357910-3AE5-2C45-A21C-9266875517DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="3" xr2:uid="{AB8518AE-64E2-2842-81B9-E381C5C00868}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="16000" xr2:uid="{AB8518AE-64E2-2842-81B9-E381C5C00868}"/>
   </bookViews>
   <sheets>
     <sheet name="Intensional Definitions" sheetId="1" r:id="rId1"/>
@@ -65,15 +65,6 @@
     <t>&lt;Mood disorder&gt;</t>
   </si>
   <si>
-    <t>psychiatric disorder constituting a category of disorders, characterized by anxious feeling or fear</t>
-  </si>
-  <si>
-    <t>psychiatric disorder constituting a category of disorders, characterized by disturbance in mood as their predominant feature</t>
-  </si>
-  <si>
-    <t>biota composed of the microorganisms (including bacteria, virus, archaea, and fungi) that exist in an organism</t>
-  </si>
-  <si>
     <t>microorganism that is unicellular, prokaryotic, and reproduces by cell division</t>
   </si>
   <si>
@@ -192,6 +183,15 @@
   </si>
   <si>
     <t>Embedded in the more general relation "is linked to"</t>
+  </si>
+  <si>
+    <t>mental disorder constituting a category of disorders, characterized by disturbance in mood as their predominant feature</t>
+  </si>
+  <si>
+    <t>mental disorder constituting a category of disorders, characterized by anxious feeling or fear</t>
+  </si>
+  <si>
+    <t>biota composed of microorganisms, including bacteria, virus, archaea and fungi, that exist in an organism</t>
   </si>
 </sst>
 </file>
@@ -270,7 +270,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -287,6 +287,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -631,10 +634,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -642,15 +645,15 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
+      <c r="B3" s="12" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -658,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -666,7 +669,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -674,7 +677,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -682,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -690,7 +693,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -698,7 +701,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -738,90 +741,90 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -857,13 +860,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -871,10 +874,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -882,10 +885,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -893,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -904,10 +907,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -915,10 +918,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -926,10 +929,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -955,112 +958,112 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
